--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/8103-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/8103-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD6F2E21-D011-4386-BD12-0BB9DDCC2097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{389FA269-A71C-4D44-9F61-F2404043436F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{19B35455-9C04-47D1-9471-DD02FB6C5EDE}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{0786F577-A601-4382-A7CD-393AD0C907BD}"/>
   </bookViews>
   <sheets>
     <sheet name="8103-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1478,29 +1478,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2354C228-1E0C-4D10-B8A9-26CB92CA72E4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1CA39C3-80ED-419F-B2C5-40295AE9049A}">
   <dimension ref="A1:X29"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1534,7 +1533,7 @@
       <c r="W1" s="26"/>
       <c r="X1" s="18"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
@@ -1570,7 +1569,7 @@
       <c r="W2" s="28"/>
       <c r="X2" s="29"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
         <v>2</v>
       </c>
@@ -1622,7 +1621,7 @@
       </c>
       <c r="X3" s="32"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="21"/>
       <c r="B4" s="22"/>
       <c r="C4" s="7"/>
@@ -1690,7 +1689,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="33">
         <v>2024</v>
       </c>
@@ -1762,7 +1761,7 @@
         <v>8.32</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="35">
         <v>2023</v>
       </c>
@@ -1834,7 +1833,7 @@
         <v>3.04</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="33">
         <v>2022</v>
       </c>
@@ -1906,7 +1905,7 @@
         <v>6.53</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="35">
         <v>2021</v>
       </c>
@@ -1978,7 +1977,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="33">
         <v>2020</v>
       </c>
@@ -2050,7 +2049,7 @@
         <v>4.47</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2019</v>
       </c>
@@ -2122,7 +2121,7 @@
         <v>6.46</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="33">
         <v>2018</v>
       </c>
@@ -2194,7 +2193,7 @@
         <v>4.6100000000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>2017</v>
       </c>
@@ -2266,7 +2265,7 @@
         <v>4.6100000000000003</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="33">
         <v>2016</v>
       </c>
@@ -2338,7 +2337,7 @@
         <v>6.56</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>2015</v>
       </c>
@@ -2410,7 +2409,7 @@
         <v>3.29</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="33">
         <v>2014</v>
       </c>
@@ -2482,7 +2481,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2013</v>
       </c>
@@ -2554,7 +2553,7 @@
         <v>4.91</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="33">
         <v>2012</v>
       </c>
@@ -2626,7 +2625,7 @@
         <v>8.57</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>2011</v>
       </c>
@@ -2698,7 +2697,7 @@
         <v>9.7899999999999991</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="33">
         <v>2010</v>
       </c>
@@ -2770,7 +2769,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>2009</v>
       </c>
@@ -2842,7 +2841,7 @@
         <v>6.87</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="33">
         <v>2008</v>
       </c>
@@ -2914,7 +2913,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
         <v>2007</v>
       </c>
@@ -2986,7 +2985,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="33">
         <v>2006</v>
       </c>
@@ -3058,7 +3057,7 @@
         <v>7.05</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="35">
         <v>2005</v>
       </c>
@@ -3130,7 +3129,7 @@
         <v>9.2899999999999991</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="33">
         <v>2004</v>
       </c>
@@ -3202,7 +3201,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
         <v>2003</v>
       </c>
@@ -3274,7 +3273,7 @@
         <v>7.41</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="33">
         <v>2002</v>
       </c>
@@ -3346,7 +3345,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>2001</v>
       </c>
@@ -3418,7 +3417,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="33" t="s">
         <v>52</v>
       </c>
